--- a/meeting/file/25_3_30_excel.xlsx
+++ b/meeting/file/25_3_30_excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\TronclassProMax\TronclassProMax\meeting\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9596C88A-45CB-4FCD-88AF-CC7200A75CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3900C3-07C0-441E-AFA4-9BCCB3DD5EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EFC119B7-54EC-49B6-9B42-17A349AFA24D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" xr2:uid="{EFC119B7-54EC-49B6-9B42-17A349AFA24D}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>雙週期</t>
   </si>
@@ -191,9 +191,6 @@
     <t>7/21–8/3</t>
   </si>
   <si>
-    <t>準備 Demo 合約部署（Mumbai）</t>
-  </si>
-  <si>
     <t>上線至 Vercel 測試</t>
   </si>
   <si>
@@ -203,56 +200,82 @@
     <t>對外展示測試版本</t>
   </si>
   <si>
+    <t>修正測試網錯誤</t>
+  </si>
+  <si>
+    <t>與合約端完成正式整合</t>
+  </si>
+  <si>
+    <t>自動發送通知 email + log 儲存</t>
+  </si>
+  <si>
+    <t>整合所有細節問題</t>
+  </si>
+  <si>
+    <t>撰寫報告、PPT、使用手冊</t>
+  </si>
+  <si>
+    <t>錄 Demo 影片、撰說明介面</t>
+  </si>
+  <si>
+    <t>API 說明、發信記錄總結</t>
+  </si>
+  <si>
+    <t>總收尾 &amp; 期末發表準備</t>
+  </si>
+  <si>
+    <t>[ 使用者 ] ←→ [ 前端 React + ethers.js ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 ↓                      ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              [ 智能合約 Solidity ] ←→ [ IPFS ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             [ 後端 Node.js + DB + API（兌換紀錄、全文內容、發信）]</t>
+  </si>
+  <si>
+    <t>後端組（2人）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>8/4–8/17</t>
-  </si>
-  <si>
-    <t>修正測試網錯誤</t>
-  </si>
-  <si>
-    <t>與合約端完成正式整合</t>
-  </si>
-  <si>
-    <t>自動發送通知 email + log 儲存</t>
-  </si>
-  <si>
-    <t>整合所有細節問題</t>
-  </si>
-  <si>
-    <t>8/18–9/1</t>
-  </si>
-  <si>
-    <t>撰寫報告、PPT、使用手冊</t>
-  </si>
-  <si>
-    <t>錄 Demo 影片、撰說明介面</t>
-  </si>
-  <si>
-    <t>API 說明、發信記錄總結</t>
-  </si>
-  <si>
-    <t>總收尾 &amp; 期末發表準備</t>
-  </si>
-  <si>
-    <t>[ 使用者 ] ←→ [ 前端 React + ethers.js ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                 ↓                      ↑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">              [ 智能合約 Solidity ] ←→ [ IPFS ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                 ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             [ 後端 Node.js + DB + API（兌換紀錄、全文內容、發信）]</t>
-  </si>
-  <si>
-    <t>智能合約組（2人）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>後端組（2人）</t>
+    <t>完成代理執行合約與測試</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能合約組（1人）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/18–8/31</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/1~9/14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/15~9/28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/29~10/12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>準備通用部屬單元與通用呼叫單元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>與前後端橋接</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -260,7 +283,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -301,6 +324,15 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -324,7 +356,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -337,8 +369,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -674,17 +718,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0D6ED1-92CA-4C66-AE7F-6561B9254CBD}">
-  <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.109375" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
-    <col min="4" max="4" width="46.77734375" customWidth="1"/>
-    <col min="5" max="5" width="43.109375" customWidth="1"/>
-    <col min="6" max="6" width="36.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.125" customWidth="1"/>
+    <col min="3" max="3" width="48.375" customWidth="1"/>
+    <col min="4" max="4" width="46.75" customWidth="1"/>
+    <col min="5" max="5" width="43.125" customWidth="1"/>
+    <col min="6" max="6" width="36.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,65 +742,65 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -769,14 +813,14 @@
       <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -785,17 +829,17 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -804,7 +848,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="97.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -817,14 +861,14 @@
       <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -833,17 +877,17 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -852,27 +896,27 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="9" spans="1:13" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -881,14 +925,14 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -901,44 +945,44 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="12" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <v>7</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -951,78 +995,134 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="19.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="19.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>64</v>
-      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>14</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:D3"/>
@@ -1032,21 +1132,6 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
